--- a/report_4.xlsx
+++ b/report_4.xlsx
@@ -10202,7 +10202,7 @@
         <v>40589</v>
       </c>
       <c r="E2" t="n">
-        <v>5541</v>
+        <v>5546</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -10228,7 +10228,7 @@
         <v>41111</v>
       </c>
       <c r="E3" t="n">
-        <v>5019</v>
+        <v>5024</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -10254,7 +10254,7 @@
         <v>41585</v>
       </c>
       <c r="E4" t="n">
-        <v>4545</v>
+        <v>4550</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -10280,7 +10280,7 @@
         <v>41781</v>
       </c>
       <c r="E5" t="n">
-        <v>4349</v>
+        <v>4354</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -10306,7 +10306,7 @@
         <v>42026</v>
       </c>
       <c r="E6" t="n">
-        <v>4104</v>
+        <v>4109</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -10332,7 +10332,7 @@
         <v>42150</v>
       </c>
       <c r="E7" t="n">
-        <v>3980</v>
+        <v>3985</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -10358,7 +10358,7 @@
         <v>42257</v>
       </c>
       <c r="E8" t="n">
-        <v>3873</v>
+        <v>3878</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -10384,7 +10384,7 @@
         <v>42298</v>
       </c>
       <c r="E9" t="n">
-        <v>3832</v>
+        <v>3837</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -10410,7 +10410,7 @@
         <v>42335</v>
       </c>
       <c r="E10" t="n">
-        <v>3795</v>
+        <v>3800</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -10436,7 +10436,7 @@
         <v>42355</v>
       </c>
       <c r="E11" t="n">
-        <v>3775</v>
+        <v>3780</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -10462,7 +10462,7 @@
         <v>42416</v>
       </c>
       <c r="E12" t="n">
-        <v>3714</v>
+        <v>3719</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -10488,7 +10488,7 @@
         <v>42426</v>
       </c>
       <c r="E13" t="n">
-        <v>3704</v>
+        <v>3709</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -10514,7 +10514,7 @@
         <v>42446</v>
       </c>
       <c r="E14" t="n">
-        <v>3684</v>
+        <v>3689</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -10540,7 +10540,7 @@
         <v>42465</v>
       </c>
       <c r="E15" t="n">
-        <v>3665</v>
+        <v>3670</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -10566,7 +10566,7 @@
         <v>42575</v>
       </c>
       <c r="E16" t="n">
-        <v>3555</v>
+        <v>3560</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -10592,7 +10592,7 @@
         <v>42577</v>
       </c>
       <c r="E17" t="n">
-        <v>3553</v>
+        <v>3558</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -10618,7 +10618,7 @@
         <v>42581</v>
       </c>
       <c r="E18" t="n">
-        <v>3549</v>
+        <v>3554</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -10644,7 +10644,7 @@
         <v>42604</v>
       </c>
       <c r="E19" t="n">
-        <v>3526</v>
+        <v>3531</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -10670,7 +10670,7 @@
         <v>42650</v>
       </c>
       <c r="E20" t="n">
-        <v>3480</v>
+        <v>3485</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -10696,7 +10696,7 @@
         <v>42655</v>
       </c>
       <c r="E21" t="n">
-        <v>3475</v>
+        <v>3480</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -10722,7 +10722,7 @@
         <v>42666</v>
       </c>
       <c r="E22" t="n">
-        <v>3464</v>
+        <v>3469</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -10748,7 +10748,7 @@
         <v>42701</v>
       </c>
       <c r="E23" t="n">
-        <v>3429</v>
+        <v>3434</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -10774,7 +10774,7 @@
         <v>42705</v>
       </c>
       <c r="E24" t="n">
-        <v>3425</v>
+        <v>3430</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -10800,7 +10800,7 @@
         <v>42722</v>
       </c>
       <c r="E25" t="n">
-        <v>3408</v>
+        <v>3413</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -10826,7 +10826,7 @@
         <v>42732</v>
       </c>
       <c r="E26" t="n">
-        <v>3398</v>
+        <v>3403</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -10852,7 +10852,7 @@
         <v>42791</v>
       </c>
       <c r="E27" t="n">
-        <v>3339</v>
+        <v>3344</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -10878,7 +10878,7 @@
         <v>42796</v>
       </c>
       <c r="E28" t="n">
-        <v>3334</v>
+        <v>3339</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -10904,7 +10904,7 @@
         <v>42844</v>
       </c>
       <c r="E29" t="n">
-        <v>3286</v>
+        <v>3291</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -10930,7 +10930,7 @@
         <v>42847</v>
       </c>
       <c r="E30" t="n">
-        <v>3283</v>
+        <v>3288</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -10956,7 +10956,7 @@
         <v>42878</v>
       </c>
       <c r="E31" t="n">
-        <v>3252</v>
+        <v>3257</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -10982,7 +10982,7 @@
         <v>42890</v>
       </c>
       <c r="E32" t="n">
-        <v>3240</v>
+        <v>3245</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -11008,7 +11008,7 @@
         <v>42906</v>
       </c>
       <c r="E33" t="n">
-        <v>3224</v>
+        <v>3229</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -11034,7 +11034,7 @@
         <v>42963</v>
       </c>
       <c r="E34" t="n">
-        <v>3167</v>
+        <v>3172</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -11060,7 +11060,7 @@
         <v>43019</v>
       </c>
       <c r="E35" t="n">
-        <v>3111</v>
+        <v>3116</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -11086,7 +11086,7 @@
         <v>43035</v>
       </c>
       <c r="E36" t="n">
-        <v>3095</v>
+        <v>3100</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -11112,7 +11112,7 @@
         <v>43097</v>
       </c>
       <c r="E37" t="n">
-        <v>3033</v>
+        <v>3038</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -11138,7 +11138,7 @@
         <v>43184</v>
       </c>
       <c r="E38" t="n">
-        <v>2946</v>
+        <v>2951</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -11164,7 +11164,7 @@
         <v>43196</v>
       </c>
       <c r="E39" t="n">
-        <v>2934</v>
+        <v>2939</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -11190,7 +11190,7 @@
         <v>43204</v>
       </c>
       <c r="E40" t="n">
-        <v>2926</v>
+        <v>2931</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -11216,7 +11216,7 @@
         <v>43235</v>
       </c>
       <c r="E41" t="n">
-        <v>2895</v>
+        <v>2900</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -11242,7 +11242,7 @@
         <v>43241</v>
       </c>
       <c r="E42" t="n">
-        <v>2889</v>
+        <v>2894</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -11268,7 +11268,7 @@
         <v>43267</v>
       </c>
       <c r="E43" t="n">
-        <v>2863</v>
+        <v>2868</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -11294,7 +11294,7 @@
         <v>43279</v>
       </c>
       <c r="E44" t="n">
-        <v>2851</v>
+        <v>2856</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -11320,7 +11320,7 @@
         <v>43307</v>
       </c>
       <c r="E45" t="n">
-        <v>2823</v>
+        <v>2828</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -11346,7 +11346,7 @@
         <v>43319</v>
       </c>
       <c r="E46" t="n">
-        <v>2811</v>
+        <v>2816</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -11372,7 +11372,7 @@
         <v>43330</v>
       </c>
       <c r="E47" t="n">
-        <v>2800</v>
+        <v>2805</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -11398,7 +11398,7 @@
         <v>43342</v>
       </c>
       <c r="E48" t="n">
-        <v>2788</v>
+        <v>2793</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -11424,7 +11424,7 @@
         <v>43343</v>
       </c>
       <c r="E49" t="n">
-        <v>2787</v>
+        <v>2792</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -11450,7 +11450,7 @@
         <v>43355</v>
       </c>
       <c r="E50" t="n">
-        <v>2775</v>
+        <v>2780</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -11476,7 +11476,7 @@
         <v>43384</v>
       </c>
       <c r="E51" t="n">
-        <v>2746</v>
+        <v>2751</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -11502,7 +11502,7 @@
         <v>43406</v>
       </c>
       <c r="E52" t="n">
-        <v>2724</v>
+        <v>2729</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -11528,7 +11528,7 @@
         <v>43429</v>
       </c>
       <c r="E53" t="n">
-        <v>2701</v>
+        <v>2706</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -11554,7 +11554,7 @@
         <v>43506</v>
       </c>
       <c r="E54" t="n">
-        <v>2624</v>
+        <v>2629</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -11580,7 +11580,7 @@
         <v>43527</v>
       </c>
       <c r="E55" t="n">
-        <v>2603</v>
+        <v>2608</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -11606,7 +11606,7 @@
         <v>43533</v>
       </c>
       <c r="E56" t="n">
-        <v>2597</v>
+        <v>2602</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -11632,7 +11632,7 @@
         <v>43538</v>
       </c>
       <c r="E57" t="n">
-        <v>2592</v>
+        <v>2597</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -11658,7 +11658,7 @@
         <v>43543</v>
       </c>
       <c r="E58" t="n">
-        <v>2587</v>
+        <v>2592</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -11684,7 +11684,7 @@
         <v>43554</v>
       </c>
       <c r="E59" t="n">
-        <v>2576</v>
+        <v>2581</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -11710,7 +11710,7 @@
         <v>43559</v>
       </c>
       <c r="E60" t="n">
-        <v>2571</v>
+        <v>2576</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -11736,7 +11736,7 @@
         <v>43586</v>
       </c>
       <c r="E61" t="n">
-        <v>2544</v>
+        <v>2549</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -11762,7 +11762,7 @@
         <v>43591</v>
       </c>
       <c r="E62" t="n">
-        <v>2539</v>
+        <v>2544</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -11788,7 +11788,7 @@
         <v>43649</v>
       </c>
       <c r="E63" t="n">
-        <v>2481</v>
+        <v>2486</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>43688</v>
       </c>
       <c r="E64" t="n">
-        <v>2442</v>
+        <v>2447</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -11840,7 +11840,7 @@
         <v>43723</v>
       </c>
       <c r="E65" t="n">
-        <v>2407</v>
+        <v>2412</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -11866,7 +11866,7 @@
         <v>43734</v>
       </c>
       <c r="E66" t="n">
-        <v>2396</v>
+        <v>2401</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -11892,7 +11892,7 @@
         <v>43777</v>
       </c>
       <c r="E67" t="n">
-        <v>2353</v>
+        <v>2358</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>43781</v>
       </c>
       <c r="E68" t="n">
-        <v>2349</v>
+        <v>2354</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -11944,7 +11944,7 @@
         <v>43803</v>
       </c>
       <c r="E69" t="n">
-        <v>2327</v>
+        <v>2332</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -11970,7 +11970,7 @@
         <v>43818</v>
       </c>
       <c r="E70" t="n">
-        <v>2312</v>
+        <v>2317</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -11996,7 +11996,7 @@
         <v>43833</v>
       </c>
       <c r="E71" t="n">
-        <v>2297</v>
+        <v>2302</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -12022,7 +12022,7 @@
         <v>43871</v>
       </c>
       <c r="E72" t="n">
-        <v>2259</v>
+        <v>2264</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -12048,7 +12048,7 @@
         <v>43919</v>
       </c>
       <c r="E73" t="n">
-        <v>2211</v>
+        <v>2216</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -12074,7 +12074,7 @@
         <v>43958</v>
       </c>
       <c r="E74" t="n">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -12100,7 +12100,7 @@
         <v>44001</v>
       </c>
       <c r="E75" t="n">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -12126,7 +12126,7 @@
         <v>44001</v>
       </c>
       <c r="E76" t="n">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -12152,7 +12152,7 @@
         <v>44001</v>
       </c>
       <c r="E77" t="n">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>44029</v>
       </c>
       <c r="E78" t="n">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -12204,7 +12204,7 @@
         <v>44055</v>
       </c>
       <c r="E79" t="n">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -12230,7 +12230,7 @@
         <v>44062</v>
       </c>
       <c r="E80" t="n">
-        <v>2068</v>
+        <v>2073</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -12256,7 +12256,7 @@
         <v>44089</v>
       </c>
       <c r="E81" t="n">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -12282,7 +12282,7 @@
         <v>44096</v>
       </c>
       <c r="E82" t="n">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -12308,7 +12308,7 @@
         <v>44108</v>
       </c>
       <c r="E83" t="n">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -12334,7 +12334,7 @@
         <v>44118</v>
       </c>
       <c r="E84" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -12360,7 +12360,7 @@
         <v>44130</v>
       </c>
       <c r="E85" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -12386,7 +12386,7 @@
         <v>44133</v>
       </c>
       <c r="E86" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -12412,7 +12412,7 @@
         <v>44142</v>
       </c>
       <c r="E87" t="n">
-        <v>1988</v>
+        <v>1993</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -12438,7 +12438,7 @@
         <v>44142</v>
       </c>
       <c r="E88" t="n">
-        <v>1988</v>
+        <v>1993</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
@@ -12464,7 +12464,7 @@
         <v>44157</v>
       </c>
       <c r="E89" t="n">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         <v>44160</v>
       </c>
       <c r="E90" t="n">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
@@ -12516,7 +12516,7 @@
         <v>44183</v>
       </c>
       <c r="E91" t="n">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
@@ -12542,7 +12542,7 @@
         <v>44207</v>
       </c>
       <c r="E92" t="n">
-        <v>1923</v>
+        <v>1928</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
@@ -12568,7 +12568,7 @@
         <v>44231</v>
       </c>
       <c r="E93" t="n">
-        <v>1899</v>
+        <v>1904</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -12594,7 +12594,7 @@
         <v>44242</v>
       </c>
       <c r="E94" t="n">
-        <v>1888</v>
+        <v>1893</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
@@ -12620,7 +12620,7 @@
         <v>44269</v>
       </c>
       <c r="E95" t="n">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="F95" t="b">
         <v>1</v>
@@ -12646,7 +12646,7 @@
         <v>44289</v>
       </c>
       <c r="E96" t="n">
-        <v>1841</v>
+        <v>1846</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
@@ -12672,7 +12672,7 @@
         <v>44302</v>
       </c>
       <c r="E97" t="n">
-        <v>1828</v>
+        <v>1833</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
@@ -12698,7 +12698,7 @@
         <v>44323</v>
       </c>
       <c r="E98" t="n">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
@@ -12724,7 +12724,7 @@
         <v>44346</v>
       </c>
       <c r="E99" t="n">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
@@ -12750,7 +12750,7 @@
         <v>44355</v>
       </c>
       <c r="E100" t="n">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -12776,7 +12776,7 @@
         <v>44371</v>
       </c>
       <c r="E101" t="n">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
@@ -12802,7 +12802,7 @@
         <v>44398</v>
       </c>
       <c r="E102" t="n">
-        <v>1732</v>
+        <v>1737</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
@@ -12828,7 +12828,7 @@
         <v>44398</v>
       </c>
       <c r="E103" t="n">
-        <v>1732</v>
+        <v>1737</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
@@ -12854,7 +12854,7 @@
         <v>44411</v>
       </c>
       <c r="E104" t="n">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -12880,7 +12880,7 @@
         <v>44416</v>
       </c>
       <c r="E105" t="n">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
@@ -12906,7 +12906,7 @@
         <v>44421</v>
       </c>
       <c r="E106" t="n">
-        <v>1709</v>
+        <v>1714</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
@@ -12932,7 +12932,7 @@
         <v>44431</v>
       </c>
       <c r="E107" t="n">
-        <v>1699</v>
+        <v>1704</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -12958,7 +12958,7 @@
         <v>44444</v>
       </c>
       <c r="E108" t="n">
-        <v>1686</v>
+        <v>1691</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
@@ -12984,7 +12984,7 @@
         <v>44466</v>
       </c>
       <c r="E109" t="n">
-        <v>1664</v>
+        <v>1669</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
@@ -13010,7 +13010,7 @@
         <v>44473</v>
       </c>
       <c r="E110" t="n">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
@@ -13036,7 +13036,7 @@
         <v>44476</v>
       </c>
       <c r="E111" t="n">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
@@ -13062,7 +13062,7 @@
         <v>44488</v>
       </c>
       <c r="E112" t="n">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
@@ -13088,7 +13088,7 @@
         <v>44492</v>
       </c>
       <c r="E113" t="n">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="F113" t="b">
         <v>1</v>
@@ -13114,7 +13114,7 @@
         <v>44493</v>
       </c>
       <c r="E114" t="n">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
@@ -13140,7 +13140,7 @@
         <v>44554</v>
       </c>
       <c r="E115" t="n">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
@@ -13166,7 +13166,7 @@
         <v>44557</v>
       </c>
       <c r="E116" t="n">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="F116" t="b">
         <v>1</v>
@@ -13192,7 +13192,7 @@
         <v>44561</v>
       </c>
       <c r="E117" t="n">
-        <v>1569</v>
+        <v>1574</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
@@ -13218,7 +13218,7 @@
         <v>44578</v>
       </c>
       <c r="E118" t="n">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
@@ -13244,7 +13244,7 @@
         <v>44590</v>
       </c>
       <c r="E119" t="n">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
@@ -13270,7 +13270,7 @@
         <v>44605</v>
       </c>
       <c r="E120" t="n">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
@@ -13296,7 +13296,7 @@
         <v>44653</v>
       </c>
       <c r="E121" t="n">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
@@ -13322,7 +13322,7 @@
         <v>44662</v>
       </c>
       <c r="E122" t="n">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
@@ -13348,7 +13348,7 @@
         <v>44677</v>
       </c>
       <c r="E123" t="n">
-        <v>1453</v>
+        <v>1458</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         <v>44682</v>
       </c>
       <c r="E124" t="n">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
@@ -13400,7 +13400,7 @@
         <v>44711</v>
       </c>
       <c r="E125" t="n">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
@@ -13426,7 +13426,7 @@
         <v>44733</v>
       </c>
       <c r="E126" t="n">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
@@ -13452,7 +13452,7 @@
         <v>44734</v>
       </c>
       <c r="E127" t="n">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
@@ -13478,7 +13478,7 @@
         <v>44735</v>
       </c>
       <c r="E128" t="n">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
@@ -13504,7 +13504,7 @@
         <v>44746</v>
       </c>
       <c r="E129" t="n">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
@@ -13530,7 +13530,7 @@
         <v>44755</v>
       </c>
       <c r="E130" t="n">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
@@ -13556,7 +13556,7 @@
         <v>44757</v>
       </c>
       <c r="E131" t="n">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
@@ -13582,7 +13582,7 @@
         <v>44777</v>
       </c>
       <c r="E132" t="n">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
@@ -13608,7 +13608,7 @@
         <v>44783</v>
       </c>
       <c r="E133" t="n">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
@@ -13634,7 +13634,7 @@
         <v>44784</v>
       </c>
       <c r="E134" t="n">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="F134" t="b">
         <v>1</v>
@@ -13660,7 +13660,7 @@
         <v>44784</v>
       </c>
       <c r="E135" t="n">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
@@ -13686,7 +13686,7 @@
         <v>44792</v>
       </c>
       <c r="E136" t="n">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="F136" t="b">
         <v>1</v>
@@ -13712,7 +13712,7 @@
         <v>44794</v>
       </c>
       <c r="E137" t="n">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
@@ -13738,7 +13738,7 @@
         <v>44796</v>
       </c>
       <c r="E138" t="n">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
@@ -13764,7 +13764,7 @@
         <v>44821</v>
       </c>
       <c r="E139" t="n">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
@@ -13790,7 +13790,7 @@
         <v>44833</v>
       </c>
       <c r="E140" t="n">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
@@ -13816,7 +13816,7 @@
         <v>44834</v>
       </c>
       <c r="E141" t="n">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
@@ -13842,7 +13842,7 @@
         <v>44854</v>
       </c>
       <c r="E142" t="n">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
@@ -13868,7 +13868,7 @@
         <v>44890</v>
       </c>
       <c r="E143" t="n">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
@@ -13894,7 +13894,7 @@
         <v>44903</v>
       </c>
       <c r="E144" t="n">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
@@ -13920,7 +13920,7 @@
         <v>44914</v>
       </c>
       <c r="E145" t="n">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
@@ -13946,7 +13946,7 @@
         <v>44929</v>
       </c>
       <c r="E146" t="n">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
@@ -13972,7 +13972,7 @@
         <v>44947</v>
       </c>
       <c r="E147" t="n">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="F147" t="b">
         <v>1</v>
@@ -13998,7 +13998,7 @@
         <v>44952</v>
       </c>
       <c r="E148" t="n">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -14024,7 +14024,7 @@
         <v>44955</v>
       </c>
       <c r="E149" t="n">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
@@ -14050,7 +14050,7 @@
         <v>44967</v>
       </c>
       <c r="E150" t="n">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
@@ -14076,7 +14076,7 @@
         <v>44975</v>
       </c>
       <c r="E151" t="n">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -14102,7 +14102,7 @@
         <v>44983</v>
       </c>
       <c r="E152" t="n">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="F152" t="b">
         <v>1</v>
@@ -14128,7 +14128,7 @@
         <v>44988</v>
       </c>
       <c r="E153" t="n">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="F153" t="b">
         <v>1</v>
@@ -14154,7 +14154,7 @@
         <v>44989</v>
       </c>
       <c r="E154" t="n">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="F154" t="b">
         <v>1</v>
@@ -14180,7 +14180,7 @@
         <v>45000</v>
       </c>
       <c r="E155" t="n">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="F155" t="b">
         <v>1</v>
@@ -14206,7 +14206,7 @@
         <v>45006</v>
       </c>
       <c r="E156" t="n">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="F156" t="b">
         <v>1</v>
@@ -14232,7 +14232,7 @@
         <v>45017</v>
       </c>
       <c r="E157" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F157" t="b">
         <v>1</v>
@@ -14258,7 +14258,7 @@
         <v>45018</v>
       </c>
       <c r="E158" t="n">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="F158" t="b">
         <v>1</v>
@@ -14284,7 +14284,7 @@
         <v>45021</v>
       </c>
       <c r="E159" t="n">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
@@ -14310,7 +14310,7 @@
         <v>45052</v>
       </c>
       <c r="E160" t="n">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
@@ -14336,7 +14336,7 @@
         <v>45060</v>
       </c>
       <c r="E161" t="n">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="F161" t="b">
         <v>1</v>
@@ -14362,7 +14362,7 @@
         <v>45063</v>
       </c>
       <c r="E162" t="n">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="F162" t="b">
         <v>1</v>
@@ -14388,7 +14388,7 @@
         <v>45066</v>
       </c>
       <c r="E163" t="n">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="F163" t="b">
         <v>1</v>
@@ -14414,7 +14414,7 @@
         <v>45084</v>
       </c>
       <c r="E164" t="n">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="F164" t="b">
         <v>1</v>
@@ -14440,7 +14440,7 @@
         <v>45085</v>
       </c>
       <c r="E165" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
@@ -14466,7 +14466,7 @@
         <v>45088</v>
       </c>
       <c r="E166" t="n">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
@@ -14492,7 +14492,7 @@
         <v>45112</v>
       </c>
       <c r="E167" t="n">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="F167" t="b">
         <v>1</v>
@@ -14518,7 +14518,7 @@
         <v>45112</v>
       </c>
       <c r="E168" t="n">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="F168" t="b">
         <v>1</v>
@@ -14544,7 +14544,7 @@
         <v>45113</v>
       </c>
       <c r="E169" t="n">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="F169" t="b">
         <v>1</v>
@@ -14570,7 +14570,7 @@
         <v>45120</v>
       </c>
       <c r="E170" t="n">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="F170" t="b">
         <v>1</v>
@@ -14596,7 +14596,7 @@
         <v>45127</v>
       </c>
       <c r="E171" t="n">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="F171" t="b">
         <v>1</v>
@@ -14622,7 +14622,7 @@
         <v>45129</v>
       </c>
       <c r="E172" t="n">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="F172" t="b">
         <v>1</v>
@@ -14648,7 +14648,7 @@
         <v>45130</v>
       </c>
       <c r="E173" t="n">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="F173" t="b">
         <v>1</v>
@@ -14674,7 +14674,7 @@
         <v>45133</v>
       </c>
       <c r="E174" t="n">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="F174" t="b">
         <v>1</v>
@@ -14700,7 +14700,7 @@
         <v>45136</v>
       </c>
       <c r="E175" t="n">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="F175" t="b">
         <v>1</v>
@@ -14726,7 +14726,7 @@
         <v>45148</v>
       </c>
       <c r="E176" t="n">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="F176" t="b">
         <v>1</v>
@@ -14752,7 +14752,7 @@
         <v>45164</v>
       </c>
       <c r="E177" t="n">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="F177" t="b">
         <v>1</v>
@@ -14778,7 +14778,7 @@
         <v>45171</v>
       </c>
       <c r="E178" t="n">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="F178" t="b">
         <v>1</v>
@@ -14804,7 +14804,7 @@
         <v>45175</v>
       </c>
       <c r="E179" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="F179" t="b">
         <v>1</v>
@@ -14830,7 +14830,7 @@
         <v>45203</v>
       </c>
       <c r="E180" t="n">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="F180" t="b">
         <v>1</v>
@@ -14856,7 +14856,7 @@
         <v>45213</v>
       </c>
       <c r="E181" t="n">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="F181" t="b">
         <v>1</v>
@@ -14882,7 +14882,7 @@
         <v>45214</v>
       </c>
       <c r="E182" t="n">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
@@ -14908,7 +14908,7 @@
         <v>45217</v>
       </c>
       <c r="E183" t="n">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="F183" t="b">
         <v>1</v>
@@ -14934,7 +14934,7 @@
         <v>45224</v>
       </c>
       <c r="E184" t="n">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="F184" t="b">
         <v>1</v>
@@ -14960,7 +14960,7 @@
         <v>45239</v>
       </c>
       <c r="E185" t="n">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="F185" t="b">
         <v>1</v>
@@ -14986,7 +14986,7 @@
         <v>45245</v>
       </c>
       <c r="E186" t="n">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
@@ -15012,7 +15012,7 @@
         <v>45256</v>
       </c>
       <c r="E187" t="n">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
@@ -15038,7 +15038,7 @@
         <v>45257</v>
       </c>
       <c r="E188" t="n">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="F188" t="b">
         <v>1</v>
@@ -15064,7 +15064,7 @@
         <v>45263</v>
       </c>
       <c r="E189" t="n">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -15090,7 +15090,7 @@
         <v>45281</v>
       </c>
       <c r="E190" t="n">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -15116,7 +15116,7 @@
         <v>45284</v>
       </c>
       <c r="E191" t="n">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="F191" t="b">
         <v>1</v>
@@ -15142,7 +15142,7 @@
         <v>45288</v>
       </c>
       <c r="E192" t="n">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="F192" t="b">
         <v>1</v>
@@ -15168,7 +15168,7 @@
         <v>45301</v>
       </c>
       <c r="E193" t="n">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="F193" t="b">
         <v>1</v>
@@ -15194,7 +15194,7 @@
         <v>45324</v>
       </c>
       <c r="E194" t="n">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="F194" t="b">
         <v>1</v>
@@ -15220,7 +15220,7 @@
         <v>45328</v>
       </c>
       <c r="E195" t="n">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -15246,7 +15246,7 @@
         <v>45331</v>
       </c>
       <c r="E196" t="n">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
@@ -15272,7 +15272,7 @@
         <v>45341</v>
       </c>
       <c r="E197" t="n">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -15298,7 +15298,7 @@
         <v>45364</v>
       </c>
       <c r="E198" t="n">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -15324,7 +15324,7 @@
         <v>45389</v>
       </c>
       <c r="E199" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -15350,7 +15350,7 @@
         <v>45394</v>
       </c>
       <c r="E200" t="n">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -15376,7 +15376,7 @@
         <v>45395</v>
       </c>
       <c r="E201" t="n">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -15402,7 +15402,7 @@
         <v>45399</v>
       </c>
       <c r="E202" t="n">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -15428,7 +15428,7 @@
         <v>45411</v>
       </c>
       <c r="E203" t="n">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -15454,7 +15454,7 @@
         <v>45412</v>
       </c>
       <c r="E204" t="n">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -15480,7 +15480,7 @@
         <v>45417</v>
       </c>
       <c r="E205" t="n">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="F205" t="b">
         <v>1</v>
@@ -15506,7 +15506,7 @@
         <v>45419</v>
       </c>
       <c r="E206" t="n">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="F206" t="b">
         <v>1</v>
@@ -15532,7 +15532,7 @@
         <v>45424</v>
       </c>
       <c r="E207" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
@@ -15558,7 +15558,7 @@
         <v>45431</v>
       </c>
       <c r="E208" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F208" t="b">
         <v>1</v>
@@ -15584,7 +15584,7 @@
         <v>45440</v>
       </c>
       <c r="E209" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
@@ -15610,7 +15610,7 @@
         <v>45443</v>
       </c>
       <c r="E210" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
@@ -15636,7 +15636,7 @@
         <v>45469</v>
       </c>
       <c r="E211" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="F211" t="b">
         <v>1</v>
@@ -15662,7 +15662,7 @@
         <v>45470</v>
       </c>
       <c r="E212" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="F212" t="b">
         <v>1</v>
@@ -15688,7 +15688,7 @@
         <v>45483</v>
       </c>
       <c r="E213" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F213" t="b">
         <v>1</v>
@@ -15714,7 +15714,7 @@
         <v>45485</v>
       </c>
       <c r="E214" t="n">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
@@ -15740,7 +15740,7 @@
         <v>45490</v>
       </c>
       <c r="E215" t="n">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="F215" t="b">
         <v>1</v>
@@ -15766,7 +15766,7 @@
         <v>45511</v>
       </c>
       <c r="E216" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F216" t="b">
         <v>1</v>
@@ -15792,7 +15792,7 @@
         <v>45518</v>
       </c>
       <c r="E217" t="n">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
@@ -15818,7 +15818,7 @@
         <v>45522</v>
       </c>
       <c r="E218" t="n">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F218" t="b">
         <v>1</v>
@@ -15844,7 +15844,7 @@
         <v>45526</v>
       </c>
       <c r="E219" t="n">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F219" t="b">
         <v>1</v>
@@ -15870,7 +15870,7 @@
         <v>45537</v>
       </c>
       <c r="E220" t="n">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
@@ -15896,7 +15896,7 @@
         <v>45542</v>
       </c>
       <c r="E221" t="n">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
@@ -15922,7 +15922,7 @@
         <v>45545</v>
       </c>
       <c r="E222" t="n">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -15948,7 +15948,7 @@
         <v>45576</v>
       </c>
       <c r="E223" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
@@ -15974,7 +15974,7 @@
         <v>45576</v>
       </c>
       <c r="E224" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F224" t="b">
         <v>1</v>
@@ -16000,7 +16000,7 @@
         <v>45579</v>
       </c>
       <c r="E225" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
@@ -16026,7 +16026,7 @@
         <v>45581</v>
       </c>
       <c r="E226" t="n">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
@@ -16052,7 +16052,7 @@
         <v>45581</v>
       </c>
       <c r="E227" t="n">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
@@ -16078,7 +16078,7 @@
         <v>45587</v>
       </c>
       <c r="E228" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -16104,7 +16104,7 @@
         <v>45592</v>
       </c>
       <c r="E229" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
@@ -16130,7 +16130,7 @@
         <v>45597</v>
       </c>
       <c r="E230" t="n">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F230" t="b">
         <v>1</v>
@@ -16156,7 +16156,7 @@
         <v>45608</v>
       </c>
       <c r="E231" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F231" t="b">
         <v>1</v>
@@ -16182,7 +16182,7 @@
         <v>45613</v>
       </c>
       <c r="E232" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F232" t="b">
         <v>1</v>
@@ -16208,7 +16208,7 @@
         <v>45619</v>
       </c>
       <c r="E233" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F233" t="b">
         <v>1</v>
@@ -16234,7 +16234,7 @@
         <v>45622</v>
       </c>
       <c r="E234" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
@@ -16260,7 +16260,7 @@
         <v>45641</v>
       </c>
       <c r="E235" t="n">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
@@ -16286,7 +16286,7 @@
         <v>45643</v>
       </c>
       <c r="E236" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="F236" t="b">
         <v>1</v>
@@ -16312,7 +16312,7 @@
         <v>45651</v>
       </c>
       <c r="E237" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F237" t="b">
         <v>1</v>
@@ -16338,7 +16338,7 @@
         <v>45652</v>
       </c>
       <c r="E238" t="n">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -16364,7 +16364,7 @@
         <v>45667</v>
       </c>
       <c r="E239" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F239" t="b">
         <v>1</v>
@@ -16390,7 +16390,7 @@
         <v>45668</v>
       </c>
       <c r="E240" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
@@ -16416,7 +16416,7 @@
         <v>45673</v>
       </c>
       <c r="E241" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
@@ -16442,7 +16442,7 @@
         <v>45685</v>
       </c>
       <c r="E242" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
@@ -16468,7 +16468,7 @@
         <v>45687</v>
       </c>
       <c r="E243" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
@@ -16494,7 +16494,7 @@
         <v>45687</v>
       </c>
       <c r="E244" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -16520,7 +16520,7 @@
         <v>45689</v>
       </c>
       <c r="E245" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F245" t="b">
         <v>1</v>
@@ -16546,7 +16546,7 @@
         <v>45696</v>
       </c>
       <c r="E246" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
@@ -16572,7 +16572,7 @@
         <v>45702</v>
       </c>
       <c r="E247" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F247" t="b">
         <v>1</v>
@@ -16598,7 +16598,7 @@
         <v>45713</v>
       </c>
       <c r="E248" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F248" t="b">
         <v>1</v>
@@ -16624,7 +16624,7 @@
         <v>45720</v>
       </c>
       <c r="E249" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F249" t="b">
         <v>1</v>
@@ -16650,7 +16650,7 @@
         <v>45730</v>
       </c>
       <c r="E250" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
@@ -16676,7 +16676,7 @@
         <v>45734</v>
       </c>
       <c r="E251" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
@@ -16702,7 +16702,7 @@
         <v>45744</v>
       </c>
       <c r="E252" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F252" t="b">
         <v>1</v>
@@ -16728,7 +16728,7 @@
         <v>45745</v>
       </c>
       <c r="E253" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F253" t="b">
         <v>1</v>
@@ -16754,7 +16754,7 @@
         <v>45750</v>
       </c>
       <c r="E254" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F254" t="b">
         <v>1</v>
@@ -16780,7 +16780,7 @@
         <v>45753</v>
       </c>
       <c r="E255" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F255" t="b">
         <v>1</v>
@@ -16806,7 +16806,7 @@
         <v>45758</v>
       </c>
       <c r="E256" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F256" t="b">
         <v>1</v>
@@ -16832,7 +16832,7 @@
         <v>45763</v>
       </c>
       <c r="E257" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F257" t="b">
         <v>1</v>
@@ -16858,7 +16858,7 @@
         <v>45771</v>
       </c>
       <c r="E258" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F258" t="b">
         <v>0</v>
@@ -16884,7 +16884,7 @@
         <v>45773</v>
       </c>
       <c r="E259" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F259" t="b">
         <v>0</v>
@@ -16910,7 +16910,7 @@
         <v>45776</v>
       </c>
       <c r="E260" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F260" t="b">
         <v>0</v>
@@ -16936,7 +16936,7 @@
         <v>45779</v>
       </c>
       <c r="E261" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F261" t="b">
         <v>0</v>
@@ -16962,7 +16962,7 @@
         <v>45784</v>
       </c>
       <c r="E262" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F262" t="b">
         <v>0</v>
@@ -16988,7 +16988,7 @@
         <v>45788</v>
       </c>
       <c r="E263" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F263" t="b">
         <v>0</v>
@@ -17014,7 +17014,7 @@
         <v>45798</v>
       </c>
       <c r="E264" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F264" t="b">
         <v>0</v>
@@ -17040,7 +17040,7 @@
         <v>45798</v>
       </c>
       <c r="E265" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F265" t="b">
         <v>0</v>
@@ -17066,7 +17066,7 @@
         <v>45806</v>
       </c>
       <c r="E266" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F266" t="b">
         <v>0</v>
@@ -17092,7 +17092,7 @@
         <v>45807</v>
       </c>
       <c r="E267" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F267" t="b">
         <v>0</v>
@@ -17118,7 +17118,7 @@
         <v>45810</v>
       </c>
       <c r="E268" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F268" t="b">
         <v>0</v>
@@ -17144,7 +17144,7 @@
         <v>45821</v>
       </c>
       <c r="E269" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F269" t="b">
         <v>0</v>
@@ -17170,7 +17170,7 @@
         <v>45824</v>
       </c>
       <c r="E270" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F270" t="b">
         <v>0</v>
@@ -17196,7 +17196,7 @@
         <v>45826</v>
       </c>
       <c r="E271" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F271" t="b">
         <v>0</v>
@@ -17222,7 +17222,7 @@
         <v>45829</v>
       </c>
       <c r="E272" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F272" t="b">
         <v>0</v>
@@ -17248,7 +17248,7 @@
         <v>45835</v>
       </c>
       <c r="E273" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F273" t="b">
         <v>0</v>
@@ -17274,7 +17274,7 @@
         <v>45836</v>
       </c>
       <c r="E274" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F274" t="b">
         <v>0</v>
@@ -17300,7 +17300,7 @@
         <v>45848</v>
       </c>
       <c r="E275" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F275" t="b">
         <v>0</v>
@@ -17326,7 +17326,7 @@
         <v>45848</v>
       </c>
       <c r="E276" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F276" t="b">
         <v>0</v>
@@ -17352,7 +17352,7 @@
         <v>45849</v>
       </c>
       <c r="E277" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F277" t="b">
         <v>0</v>
@@ -17378,7 +17378,7 @@
         <v>45852</v>
       </c>
       <c r="E278" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F278" t="b">
         <v>0</v>
@@ -17404,7 +17404,7 @@
         <v>45858</v>
       </c>
       <c r="E279" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F279" t="b">
         <v>0</v>
@@ -17430,7 +17430,7 @@
         <v>45863</v>
       </c>
       <c r="E280" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F280" t="b">
         <v>0</v>
@@ -17456,7 +17456,7 @@
         <v>45863</v>
       </c>
       <c r="E281" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F281" t="b">
         <v>0</v>
@@ -17482,7 +17482,7 @@
         <v>45881</v>
       </c>
       <c r="E282" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F282" t="b">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>45886</v>
       </c>
       <c r="E283" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F283" t="b">
         <v>0</v>
@@ -17534,7 +17534,7 @@
         <v>45893</v>
       </c>
       <c r="E284" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F284" t="b">
         <v>0</v>
@@ -17560,7 +17560,7 @@
         <v>45899</v>
       </c>
       <c r="E285" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F285" t="b">
         <v>0</v>
@@ -17586,7 +17586,7 @@
         <v>45900</v>
       </c>
       <c r="E286" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F286" t="b">
         <v>0</v>
@@ -17612,7 +17612,7 @@
         <v>45922</v>
       </c>
       <c r="E287" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F287" t="b">
         <v>0</v>
@@ -17638,7 +17638,7 @@
         <v>45922</v>
       </c>
       <c r="E288" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F288" t="b">
         <v>0</v>
@@ -17664,7 +17664,7 @@
         <v>45924</v>
       </c>
       <c r="E289" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F289" t="b">
         <v>0</v>
@@ -17690,7 +17690,7 @@
         <v>45928</v>
       </c>
       <c r="E290" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F290" t="b">
         <v>0</v>
@@ -17716,7 +17716,7 @@
         <v>45933</v>
       </c>
       <c r="E291" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F291" t="b">
         <v>0</v>
@@ -17742,7 +17742,7 @@
         <v>45937</v>
       </c>
       <c r="E292" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F292" t="b">
         <v>0</v>
@@ -17768,7 +17768,7 @@
         <v>45939</v>
       </c>
       <c r="E293" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F293" t="b">
         <v>0</v>
@@ -17794,7 +17794,7 @@
         <v>45944</v>
       </c>
       <c r="E294" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F294" t="b">
         <v>0</v>
@@ -17820,7 +17820,7 @@
         <v>45945</v>
       </c>
       <c r="E295" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F295" t="b">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>45950</v>
       </c>
       <c r="E296" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F296" t="b">
         <v>0</v>
@@ -17872,7 +17872,7 @@
         <v>45951</v>
       </c>
       <c r="E297" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F297" t="b">
         <v>0</v>
@@ -17898,7 +17898,7 @@
         <v>45962</v>
       </c>
       <c r="E298" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F298" t="b">
         <v>0</v>
@@ -17924,7 +17924,7 @@
         <v>45968</v>
       </c>
       <c r="E299" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F299" t="b">
         <v>0</v>
@@ -17950,7 +17950,7 @@
         <v>45971</v>
       </c>
       <c r="E300" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F300" t="b">
         <v>0</v>
@@ -17976,7 +17976,7 @@
         <v>45987</v>
       </c>
       <c r="E301" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F301" t="b">
         <v>0</v>
@@ -18002,7 +18002,7 @@
         <v>45993</v>
       </c>
       <c r="E302" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F302" t="b">
         <v>0</v>
@@ -18028,7 +18028,7 @@
         <v>45998</v>
       </c>
       <c r="E303" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F303" t="b">
         <v>0</v>
@@ -18054,7 +18054,7 @@
         <v>46000</v>
       </c>
       <c r="E304" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F304" t="b">
         <v>0</v>
@@ -18080,7 +18080,7 @@
         <v>46006</v>
       </c>
       <c r="E305" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F305" t="b">
         <v>0</v>
@@ -18106,7 +18106,7 @@
         <v>46015</v>
       </c>
       <c r="E306" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F306" t="b">
         <v>0</v>
@@ -18132,7 +18132,7 @@
         <v>46021</v>
       </c>
       <c r="E307" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F307" t="b">
         <v>0</v>
@@ -18158,7 +18158,7 @@
         <v>46024</v>
       </c>
       <c r="E308" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F308" t="b">
         <v>0</v>
@@ -18184,7 +18184,7 @@
         <v>46025</v>
       </c>
       <c r="E309" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F309" t="b">
         <v>0</v>
@@ -18210,7 +18210,7 @@
         <v>46032</v>
       </c>
       <c r="E310" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F310" t="b">
         <v>0</v>
@@ -18236,7 +18236,7 @@
         <v>46036</v>
       </c>
       <c r="E311" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F311" t="b">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>46038</v>
       </c>
       <c r="E312" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F312" t="b">
         <v>0</v>
@@ -18288,7 +18288,7 @@
         <v>46038</v>
       </c>
       <c r="E313" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F313" t="b">
         <v>0</v>
@@ -18314,7 +18314,7 @@
         <v>46040</v>
       </c>
       <c r="E314" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F314" t="b">
         <v>0</v>
@@ -18340,7 +18340,7 @@
         <v>46041</v>
       </c>
       <c r="E315" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F315" t="b">
         <v>0</v>
@@ -18366,7 +18366,7 @@
         <v>46043</v>
       </c>
       <c r="E316" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F316" t="b">
         <v>0</v>
@@ -18392,7 +18392,7 @@
         <v>46048</v>
       </c>
       <c r="E317" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F317" t="b">
         <v>0</v>
@@ -18418,7 +18418,7 @@
         <v>46049</v>
       </c>
       <c r="E318" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F318" t="b">
         <v>0</v>
@@ -18444,7 +18444,7 @@
         <v>46052</v>
       </c>
       <c r="E319" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F319" t="b">
         <v>0</v>
@@ -18470,7 +18470,7 @@
         <v>46055</v>
       </c>
       <c r="E320" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F320" t="b">
         <v>0</v>
@@ -18496,7 +18496,7 @@
         <v>46055</v>
       </c>
       <c r="E321" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F321" t="b">
         <v>0</v>
@@ -18522,7 +18522,7 @@
         <v>46055</v>
       </c>
       <c r="E322" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F322" t="b">
         <v>0</v>
@@ -18548,7 +18548,7 @@
         <v>46056</v>
       </c>
       <c r="E323" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F323" t="b">
         <v>0</v>
@@ -18574,7 +18574,7 @@
         <v>46058</v>
       </c>
       <c r="E324" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F324" t="b">
         <v>0</v>
@@ -18600,7 +18600,7 @@
         <v>46058</v>
       </c>
       <c r="E325" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F325" t="b">
         <v>0</v>
@@ -18626,7 +18626,7 @@
         <v>46065</v>
       </c>
       <c r="E326" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F326" t="b">
         <v>0</v>
@@ -18652,7 +18652,7 @@
         <v>46069</v>
       </c>
       <c r="E327" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F327" t="b">
         <v>0</v>
@@ -18678,7 +18678,7 @@
         <v>46075</v>
       </c>
       <c r="E328" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F328" t="b">
         <v>0</v>
@@ -18704,7 +18704,7 @@
         <v>46077</v>
       </c>
       <c r="E329" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F329" t="b">
         <v>0</v>
@@ -18730,7 +18730,7 @@
         <v>46079</v>
       </c>
       <c r="E330" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F330" t="b">
         <v>0</v>
@@ -18756,7 +18756,7 @@
         <v>46080</v>
       </c>
       <c r="E331" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F331" t="b">
         <v>0</v>
@@ -18782,7 +18782,7 @@
         <v>46081</v>
       </c>
       <c r="E332" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F332" t="b">
         <v>0</v>
@@ -18808,7 +18808,7 @@
         <v>46085</v>
       </c>
       <c r="E333" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F333" t="b">
         <v>0</v>
@@ -18834,7 +18834,7 @@
         <v>46085</v>
       </c>
       <c r="E334" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F334" t="b">
         <v>0</v>
@@ -18860,7 +18860,7 @@
         <v>46085</v>
       </c>
       <c r="E335" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F335" t="b">
         <v>0</v>
@@ -18886,7 +18886,7 @@
         <v>46087</v>
       </c>
       <c r="E336" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F336" t="b">
         <v>0</v>
@@ -18912,7 +18912,7 @@
         <v>46105</v>
       </c>
       <c r="E337" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F337" t="b">
         <v>0</v>
@@ -34586,7 +34586,7 @@
         <v>46160</v>
       </c>
       <c r="E990" t="n">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="F990" t="b">
         <v>0</v>
@@ -34612,7 +34612,7 @@
         <v>46181</v>
       </c>
       <c r="E991" t="n">
-        <v>-51</v>
+        <v>-46</v>
       </c>
       <c r="F991" t="b">
         <v>0</v>
@@ -34638,7 +34638,7 @@
         <v>46195</v>
       </c>
       <c r="E992" t="n">
-        <v>-65</v>
+        <v>-60</v>
       </c>
       <c r="F992" t="b">
         <v>0</v>
@@ -34664,7 +34664,7 @@
         <v>46198</v>
       </c>
       <c r="E993" t="n">
-        <v>-68</v>
+        <v>-63</v>
       </c>
       <c r="F993" t="b">
         <v>0</v>
@@ -34690,7 +34690,7 @@
         <v>46199</v>
       </c>
       <c r="E994" t="n">
-        <v>-69</v>
+        <v>-64</v>
       </c>
       <c r="F994" t="b">
         <v>0</v>
@@ -34716,7 +34716,7 @@
         <v>46204</v>
       </c>
       <c r="E995" t="n">
-        <v>-74</v>
+        <v>-69</v>
       </c>
       <c r="F995" t="b">
         <v>0</v>
@@ -34742,7 +34742,7 @@
         <v>46222</v>
       </c>
       <c r="E996" t="n">
-        <v>-92</v>
+        <v>-87</v>
       </c>
       <c r="F996" t="b">
         <v>0</v>
@@ -34768,7 +34768,7 @@
         <v>46240</v>
       </c>
       <c r="E997" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -34794,7 +34794,7 @@
         <v>46285</v>
       </c>
       <c r="E998" t="n">
-        <v>-155</v>
+        <v>-150</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -34820,7 +34820,7 @@
         <v>46286</v>
       </c>
       <c r="E999" t="n">
-        <v>-156</v>
+        <v>-151</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -34846,7 +34846,7 @@
         <v>46298</v>
       </c>
       <c r="E1000" t="n">
-        <v>-168</v>
+        <v>-163</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -34872,7 +34872,7 @@
         <v>46310</v>
       </c>
       <c r="E1001" t="n">
-        <v>-180</v>
+        <v>-175</v>
       </c>
       <c r="F1001" t="b">
         <v>0</v>
@@ -34898,7 +34898,7 @@
         <v>46315</v>
       </c>
       <c r="E1002" t="n">
-        <v>-185</v>
+        <v>-180</v>
       </c>
       <c r="F1002" t="b">
         <v>0</v>
